--- a/recommend_result.xlsx
+++ b/recommend_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xxc/Desktop/xxc/拓殖大学/研究室/評価実験/video-recommend-system/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3C69B0B9D350D274A73A3011595ED87656CF1BC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_3C69B0B9D36056590F383B11595ED87656CF1BC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
